--- a/examples/cafe-checkout/testcase-pairwise.xlsx
+++ b/examples/cafe-checkout/testcase-pairwise.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="testcase-pairwise" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="meta" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,80 +421,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="39" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="39" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>MatrixID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Drink</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Sugar</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Ice</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Topping</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>PaymentMethod</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Loai</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Gherkin</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>KetQuaMongDoi</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>GhiChu</t>
         </is>
@@ -505,45 +512,50 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>TC-DBB3BE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>TraDao</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Thach</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "TraDao"
 And khách chọn size "S", đường "100", đá "30", topping "Thach"
@@ -552,8 +564,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -561,45 +573,50 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>TC-19617E</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>MatchaLatte</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>TranChau</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>EWallet</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "MatchaLatte"
 And khách chọn size "M", đường "30", đá "0", topping "TranChau"
@@ -608,8 +625,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -617,45 +634,50 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>TC-93F169</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>TraDao</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "TraDao"
 And khách chọn size "L", đường "30", đá "100", topping "None"
@@ -664,8 +686,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -673,45 +695,50 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>TC-F948DA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>CaPheSua</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>TranChau</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "CaPheSua"
 And khách chọn size "S", đường "30", đá "50", topping "TranChau"
@@ -720,8 +747,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -729,45 +756,50 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>TC-023DD2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>BacXiu</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "BacXiu"
 And khách chọn size "M", đường "100", đá "0", topping "None"
@@ -776,8 +808,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -785,45 +817,50 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>TC-9F3D75</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>BacXiu</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Thach</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>EWallet</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "BacXiu"
 And khách chọn size "S", đường "50", đá "0", topping "Thach"
@@ -832,8 +869,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -841,45 +878,50 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>TC-C50F33</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>BacXiu</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "BacXiu"
 And khách chọn size "L", đường "0", đá "0", topping "None"
@@ -888,8 +930,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -897,45 +939,50 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>TC-A2A2EE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>BacXiu</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>TranChau</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "BacXiu"
 And khách chọn size "L", đường "70", đá "0", topping "TranChau"
@@ -944,8 +991,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -953,45 +1000,50 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>TC-7A8312</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>TraDao</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Thach</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>EWallet</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "TraDao"
 And khách chọn size "M", đường "70", đá "100", topping "Thach"
@@ -1000,8 +1052,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1009,45 +1061,50 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>TC-069421</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>CaPheDen</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>EWallet</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "CaPheDen"
 And khách chọn size "L", đường "100", đá "50", topping "None"
@@ -1056,8 +1113,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1065,45 +1122,50 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>TC-51857F</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>CaPheDen</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>TranChau</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "CaPheDen"
 And khách chọn size "M", đường "70", đá "30", topping "TranChau"
@@ -1112,8 +1174,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1121,45 +1183,50 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>TC-937E6B</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>CaPheSua</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Thach</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "CaPheSua"
 And khách chọn size "S", đường "70", đá "50", topping "Thach"
@@ -1168,8 +1235,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1177,45 +1244,50 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>TC-7BCD80</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>MatchaLatte</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "MatchaLatte"
 And khách chọn size "S", đường "0", đá "30", topping "None"
@@ -1224,8 +1296,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1233,45 +1305,50 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>TC-705C64</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>MatchaLatte</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Thach</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "MatchaLatte"
 And khách chọn size "L", đường "100", đá "100", topping "Thach"
@@ -1280,8 +1357,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1289,45 +1366,50 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>TC-551083</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>MatchaLatte</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>EWallet</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "MatchaLatte"
 And khách chọn size "M", đường "70", đá "50", topping "None"
@@ -1336,8 +1418,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1345,45 +1427,50 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>TC-1E1936</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>TraDao</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>TranChau</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>EWallet</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "TraDao"
 And khách chọn size "L", đường "0", đá "100", topping "TranChau"
@@ -1392,8 +1479,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1401,45 +1488,50 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>TC-9B888D</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>BacXiu</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Thach</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>EWallet</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "BacXiu"
 And khách chọn size "L", đường "30", đá "0", topping "Thach"
@@ -1448,8 +1540,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1457,45 +1549,50 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>TC-1A5F4E</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>MatchaLatte</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>TranChau</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "MatchaLatte"
 And khách chọn size "L", đường "50", đá "30", topping "TranChau"
@@ -1504,8 +1601,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1513,45 +1610,50 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>TC-976DF2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>TraDao</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "TraDao"
 And khách chọn size "M", đường "50", đá "50", topping "None"
@@ -1560,8 +1662,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1569,45 +1671,50 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>TC-03DF7F</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>CaPheSua</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>EWallet</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "CaPheSua"
 And khách chọn size "M", đường "0", đá "0", topping "None"
@@ -1616,8 +1723,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1625,45 +1732,50 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>TC-FA8F48</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>TraDao</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Thach</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "TraDao"
 And khách chọn size "M", đường "50", đá "0", topping "Thach"
@@ -1672,8 +1784,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1681,45 +1793,50 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>TC-22FE3B</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>CaPheDen</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Thach</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "CaPheDen"
 And khách chọn size "S", đường "50", đá "100", topping "Thach"
@@ -1728,8 +1845,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1737,45 +1854,50 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>TC-F9B181</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>CaPheDen</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Thach</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>EWallet</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "CaPheDen"
 And khách chọn size "M", đường "0", đá "50", topping "Thach"
@@ -1784,8 +1906,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1793,45 +1915,50 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>TC-4AEF08</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>CaPheSua</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>TranChau</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "CaPheSua"
 And khách chọn size "L", đường "100", đá "100", topping "TranChau"
@@ -1840,8 +1967,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1849,45 +1976,50 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>TC-FCF54B</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>CaPheDen</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Thach</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "CaPheDen"
 And khách chọn size "L", đường "30", đá "0", topping "Thach"
@@ -1896,8 +2028,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1905,45 +2037,50 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>TC-477219</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>CaPheSua</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>TranChau</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "CaPheSua"
 And khách chọn size "M", đường "50", đá "100", topping "TranChau"
@@ -1952,8 +2089,8 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1961,45 +2098,50 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>TC-86CA9E</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>CaPheSua</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Thach</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>EWallet</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Pairwise</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Pairwise</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>When khách chọn đồ uống "CaPheSua"
 And khách chọn size "S", đường "30", đá "30", topping "Thach"
@@ -2008,37 +2150,42 @@
 And khách nhấn nút thanh toán</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BC-ED1511</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Số lượng = 0 không được thêm vào giỏ
 Input: Quantity = 0, các factor khác bất kỳ (vd CaPheDen/S/50/50/None)</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Hiển thị lỗi số lượng không hợp lệ; giỏ hàng vẫn trống</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Viết Gherkin/step tay ở bước gen-test</t>
         </is>
@@ -2048,32 +2195,235 @@
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BC-9EAB4A</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Không thể thanh toán khi giỏ hàng trống
 Input: Giỏ hàng rỗng, bấm "Thanh toán"</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Hiển thị lỗi giỏ hàng trống; không tạo đơn hàng</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Viết Gherkin/step tay ở bước gen-test</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>generated_at</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-09-13T14:55:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>model_file</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>checkout.model.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>model_sha1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>c9a1f4e0a07d</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>pict_cli</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pict-cli@0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>pict_stats</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Combinations:   307 | Generated tests:27 | Generation time:0:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>factors</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Drink, Size, Sugar, Ice, Topping, Quantity, PaymentMethod</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>rows_pairwise</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>rows_boundary</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>gherkin_template</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>checkout.gherkin-template.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>gherkin_template_sha1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>01e4676ca80d</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>factor_file</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>checkout.factor.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>factor_sha1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>c075326fae2d</t>
         </is>
       </c>
     </row>
